--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562433155</v>
+        <v>46157.93071597734</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93071597734</v>
+        <v>46157.93154931925</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93154931925</v>
+        <v>46157.93394131829</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394131829</v>
+        <v>46157.93709320928</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93709320928</v>
+        <v>46158.28211058765</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211058765</v>
+        <v>46158.29666309536</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29666309536</v>
+        <v>46158.29806064018</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806064018</v>
+        <v>46158.33381827847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381827847</v>
+        <v>46158.36848585897</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Тошпулатов/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36848585897</v>
+        <v>46158.37282018883</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
